--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sales Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,42 +413,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-20/2025-07-26</t>
+          <t>Ventas 2025-07-27 / 2025-08-02</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Venue Name</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Gross Sales</t>
-        </is>
-      </c>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Net Sales</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Discounts</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Voids</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Bill Count</t>
@@ -458,155 +446,145 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>#001 Florida Mall Orlando FL</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>24348.45</v>
-      </c>
+          <t>Alicante</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>24348.45</v>
-      </c>
-      <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="n">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
         <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1558</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>#002 American Dream Mall NJ</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>18719.53</v>
-      </c>
+          <t>Barcelona 1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>18719.53</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
+        <v>48635.51</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>1209</v>
+        <v>5093</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>#003 Sawgrass Mills Mall FL</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>30163.73</v>
-      </c>
+          <t>Barcelona 2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>30163.73</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
+        <v>21541.65</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>1895</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>#004 Weston Town Center FL</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>15717.48</v>
-      </c>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>15717.48</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
+        <v>9404.73</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>1004</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>#005 Vineland Orlando FL</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>5257.07</v>
-      </c>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>5257.07</v>
-      </c>
-      <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="n">
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
         <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>450</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>#006 Aventura, FL</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>8348.5</v>
-      </c>
+          <t>Málaga 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>8348.5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
+        <v>27092.36</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>493</v>
+        <v>3363</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>REPORT SUMMARY (6 entries)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>102554.76</v>
-      </c>
+          <t>Málaga 3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>102554.76</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
+        <v>11925.98</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>34531.63</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>3758</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>32327.22</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>3784</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-07-27 / 2025-08-02</t>
+          <t>Ventas 2025-08-03 / 2025-08-09</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>48635.51</v>
+        <v>51710.06</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>5093</v>
+        <v>5518</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>21541.65</v>
+        <v>22893.08</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>2575</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>9404.73</v>
+        <v>9990.41</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>1179</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>27092.36</v>
+        <v>30377.41</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>3363</v>
+        <v>3731</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>11925.98</v>
+        <v>12711.61</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>1431</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>34531.63</v>
+        <v>32136.33</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>3758</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>32327.22</v>
+        <v>35146.64</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>3784</v>
+        <v>3940</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-03 / 2025-08-09</t>
+          <t>Ventas 2025-08-10 / 2025-08-16</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>51710.06</v>
+        <v>52326.42</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>5518</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>22893.08</v>
+        <v>22112.42</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>2637</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>9990.41</v>
+        <v>12789.05</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>1233</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>30377.41</v>
+        <v>33270.97</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>3731</v>
+        <v>3936</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>12711.61</v>
+        <v>11963.46</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>1553</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>32136.33</v>
+        <v>33405.62</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>3360</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>35146.64</v>
+        <v>33086.74</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>3940</v>
+        <v>3744</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-10 / 2025-08-16</t>
+          <t>Ventas 2025-08-17 / 2025-08-23</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>52326.42</v>
+        <v>46694.59</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>5511</v>
+        <v>5125</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>22112.42</v>
+        <v>18768.52</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>2640</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>12789.05</v>
+        <v>11127.35</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>1509</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>33270.97</v>
+        <v>32425.96</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>3936</v>
+        <v>3852</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>11963.46</v>
+        <v>11996.12</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>1491</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>33405.62</v>
+        <v>32831.15</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>3397</v>
+        <v>3402</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>33086.74</v>
+        <v>33772.36</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>3744</v>
+        <v>3794</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-17 / 2025-08-23</t>
+          <t>Ventas 2025-08-24 / 2025-08-30</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>46694.59</v>
+        <v>46344.63</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>5125</v>
+        <v>5162</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>18768.52</v>
+        <v>17778.55</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>2260</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>11127.35</v>
+        <v>9839.700000000001</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>1344</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>32425.96</v>
+        <v>27925.31</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>3852</v>
+        <v>3488</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>11996.12</v>
+        <v>10712</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>1472</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>32831.15</v>
+        <v>30475.74</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>3402</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>33772.36</v>
+        <v>32398.51</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>3794</v>
+        <v>3824</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-24 / 2025-08-30</t>
+          <t>Ventas 2025-08-31 / 2025-09-06</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>46344.63</v>
+        <v>42201.23</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>5162</v>
+        <v>4990</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>17778.55</v>
+        <v>17148.27</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>2339</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>9839.700000000001</v>
+        <v>8194.99</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>1227</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>27925.31</v>
+        <v>23559.42</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>3488</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>10712</v>
+        <v>8743.42</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>1350</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>30475.74</v>
+        <v>27648.11</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>3246</v>
+        <v>2995</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>32398.51</v>
+        <v>30095.58</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>3824</v>
+        <v>3643</v>
       </c>
     </row>
   </sheetData>
